--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -520,6 +520,9 @@
       <c r="C11" t="str">
         <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -578,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189960</v>
+        <v>02.548511899610</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -524,9 +524,90 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>157_流沙_Quicksand_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="C21" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -581,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.548511899610</v>
+        <v>02.5485118996105110571491010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -604,6 +604,9 @@
         <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
 white_Trachymene Coerulea_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -662,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.5485118996105110571491010</v>
+        <v>02.5485118996105110571491012</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -605,7 +605,7 @@
 white_Trachymene Coerulea_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -665,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.5485118996105110571491012</v>
+        <v>02.54851189961051105714910120</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,9 +608,92 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>4</v>
+      </c>
+      <c r="C22" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>195_闺蜜_Alter Ego_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>5</v>
+      </c>
+      <c r="C29" t="str">
+        <v>669_大丽花 红_undefined_undefined_5stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>651_大丽花 奶油桃子_undefined_undefined_5stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>653_大丽花 黑_undefined_undefined_5stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -665,7 +748,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189961051105714910120</v>
+        <v>02.54851189961051105714910120716581271050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -690,6 +690,9 @@
       <c r="C31" t="str">
         <v>653_大丽花 黑_undefined_undefined_5stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -748,7 +751,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189961051105714910120716581271050</v>
+        <v>02.54851189961051105714910120716581271055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -694,9 +694,92 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>668_大丽花 粉_undefined_undefined_5stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>797_大菊黄_undefined_undefined_5stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>643_巧克力秋英_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>6</v>
+      </c>
+      <c r="C35" t="str">
+        <v>834_海芋黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>7</v>
+      </c>
+      <c r="C36" t="str">
+        <v>348_万年青_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>300_白星_White Gypso_ gypsophila_1kg</v>
+      </c>
+      <c r="F37" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>516_火焰兰_Crocosmia_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>428_南蛇藤_Celastrus orbiculatus _undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -751,7 +834,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189961051105714910120716581271055</v>
+        <v>02.54851189961051105714910120716581271055555315651050</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -776,6 +776,9 @@
       <c r="C41" t="str">
         <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F41" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -834,7 +837,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189961051105714910120716581271055555315651050</v>
+        <v>02.54851189961051105714910120716581271055555315651055</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-7-26.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -780,9 +780,41 @@
         <v>5</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>109_绣球国产绿_Hydrangea Colombia Green (local)_Hydrangea L._1stem</v>
+      </c>
+      <c r="F42" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F43" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>119_绣球璀璨_Hydrangea_Hydrangea L._1stem</v>
+      </c>
+      <c r="F44" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L45"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -837,7 +869,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02.54851189961051105714910120716581271055555315651055</v>
+        <v>02.5485118996105110571491012071658127105555531565105520302015</v>
       </c>
     </row>
   </sheetData>
